--- a/artfynd/A 14157-2022 artfynd.xlsx
+++ b/artfynd/A 14157-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14157-2022 artfynd.xlsx
+++ b/artfynd/A 14157-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78814285</v>
+        <v>80379191</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>937</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Intill stuga 350 m O Kastudden, Upl</t>
+          <t>Finnsjöns östra sida 580 m OSO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659082.79566673</v>
+        <v>659285</v>
       </c>
       <c r="R2" t="n">
-        <v>6695391.071712461</v>
+        <v>6695203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +767,39 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+          <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Den stora döda avbarkade grenen ligger på marken intill en asp # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Thorleif Joelson</t>
@@ -802,7 +807,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -813,15 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79238470</v>
+        <v>81946451</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,46 +829,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blandskog 500 m OSO Kastudden, Upl</t>
+          <t>Kastudden, 0,6 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659219.3655490372</v>
+        <v>659351</v>
       </c>
       <c r="R3" t="n">
-        <v>6695263.799828092</v>
+        <v>6695284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,22 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +904,35 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Henry Åkerström, Thorleif Joelson, Jörgen Sjöström, Mattias Lif</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -942,15 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79238934</v>
+        <v>750775</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,53 +954,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>2819</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövskog 675 m OSO Kastudden, Upl</t>
+          <t>Kastudden, 0,7 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659316.9674141898</v>
+        <v>659406</v>
       </c>
       <c r="R4" t="n">
-        <v>6695142.744945866</v>
+        <v>6695116</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,22 +1008,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,19 +1022,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1075,15 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79238929</v>
+        <v>80357197</v>
       </c>
       <c r="B5" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,53 +1060,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>6431</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövskog 675 m OSO Kastudden, Upl</t>
+          <t>Skog 550 m OSO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659316.9674141898</v>
+        <v>659284</v>
       </c>
       <c r="R5" t="n">
-        <v>6695142.744945866</v>
+        <v>6695218</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1161,22 +1125,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,6 +1143,11 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1197,7 +1156,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1208,15 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79238905</v>
+        <v>80379204</v>
       </c>
       <c r="B6" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,46 +1178,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222002</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövskogsdunge 600 m OSO Kastudden, Upl</t>
+          <t>Finnsjöns östra sida 620 m OSO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659316.9674141898</v>
+        <v>659323</v>
       </c>
       <c r="R6" t="n">
-        <v>6695142.744945866</v>
+        <v>6695244</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1290,22 +1243,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,6 +1261,36 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med stora aspar här och där.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1326,7 +1299,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Jörgen Sjöström</t>
+          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1337,15 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79238805</v>
+        <v>79238730</v>
       </c>
       <c r="B7" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,35 +1321,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1389,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659283.9129299698</v>
+        <v>659267</v>
       </c>
       <c r="R7" t="n">
-        <v>6695217.586262327</v>
+        <v>6695238</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,28 +1394,17 @@
           <t>2019-07-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-03</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1466,15 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79238423</v>
+        <v>78814285</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,24 +1438,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1507,21 +1467,21 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blandskog 500 m OSO Kastudden, Upl</t>
+          <t>Intill stuga 350 m O Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659219.3655490372</v>
+        <v>659083</v>
       </c>
       <c r="R8" t="n">
-        <v>6695263.799828092</v>
+        <v>6695391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,19 +1511,9 @@
           <t>2019-07-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-07-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,6 +1525,11 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1595,15 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80378569</v>
+        <v>80378561</v>
       </c>
       <c r="B9" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1643,14 +1593,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finnsjöns östra sida 690 m OSO Kastudden, Upl</t>
+          <t>Finnsjöns östra sida 760 m OSO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659365.1489732995</v>
+        <v>659395</v>
       </c>
       <c r="R9" t="n">
-        <v>6695107.703026786</v>
+        <v>6695119</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,19 +1630,9 @@
           <t>2019-10-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1729,15 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80378568</v>
+        <v>80378569</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,21 +1680,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1770,7 +1705,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1781,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659365.1489732995</v>
+        <v>659365</v>
       </c>
       <c r="R10" t="n">
-        <v>6695107.703026786</v>
+        <v>6695108</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1814,19 +1749,9 @@
           <t>2019-10-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1863,15 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80378574</v>
+        <v>100335339</v>
       </c>
       <c r="B11" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1879,53 +1799,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnsjöns östra sida 690 m OSO Kastudden, Upl</t>
+          <t>Nybron, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659365.1489732995</v>
+        <v>659185</v>
       </c>
       <c r="R11" t="n">
-        <v>6695107.703026786</v>
+        <v>6695233</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1949,22 +1855,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1973,43 +1879,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Ängslövskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80357197</v>
+        <v>2309408</v>
       </c>
       <c r="B12" t="n">
-        <v>77882</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,45 +1908,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6431</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog 550 m OSO Kastudden, Upl</t>
+          <t>Kastudden, 0,7 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>659283.9129299698</v>
+        <v>659403</v>
       </c>
       <c r="R12" t="n">
-        <v>6695217.586262327</v>
+        <v>6695109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2082,22 +1962,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-06-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,24 +1976,23 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2134,15 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80379204</v>
+        <v>79238934</v>
       </c>
       <c r="B13" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2150,48 +2014,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnsjöns östra sida 620 m OSO Kastudden, Upl</t>
+          <t>Lövskog 675 m OSO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>659322.9442295309</v>
+        <v>659317</v>
       </c>
       <c r="R13" t="n">
-        <v>6695244.067251872</v>
+        <v>6695143</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2215,22 +2084,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2243,36 +2102,6 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Ängsblandskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med stora aspar här och där.</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -2281,7 +2110,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2292,53 +2121,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>81946451</v>
+        <v>78814233</v>
       </c>
       <c r="B14" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>220204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kastudden, 0,6 km O-ut, Upl</t>
+          <t>Intill vägkors 400m NNO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>659350.9675137666</v>
+        <v>658921</v>
       </c>
       <c r="R14" t="n">
-        <v>6695283.936335549</v>
+        <v>6695724</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2365,22 +2202,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2393,35 +2220,20 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson, Jörgen Sjöström, Mattias Lif</t>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2432,15 +2244,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80379191</v>
+        <v>79238470</v>
       </c>
       <c r="B15" t="n">
-        <v>88969</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,41 +2255,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>937</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Finnsjöns östra sida 580 m OSO Kastudden, Upl</t>
+          <t>Blandskog 500 m OSO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>659285.058567494</v>
+        <v>659219</v>
       </c>
       <c r="R15" t="n">
-        <v>6695202.774785042</v>
+        <v>6695264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2509,22 +2321,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2537,41 +2339,7 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Ängslövskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Den stora döda avbarkade grenen ligger på marken intill en asp # Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
+      <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
           <t>Thorleif Joelson</t>
@@ -2579,7 +2347,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2590,55 +2358,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>100335339</v>
+        <v>79238805</v>
       </c>
       <c r="B16" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nybron, Upl</t>
+          <t>Skog 550 m OSO Kastudden, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>659185.0076964458</v>
+        <v>659284</v>
       </c>
       <c r="R16" t="n">
-        <v>6695232.571073242</v>
+        <v>6695218</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2662,22 +2435,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:01</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:01</t>
+          <t>2019-07-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2686,21 +2449,842 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>80378568</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Finnsjöns östra sida 690 m OSO Kastudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>659365</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6695108</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>79238905</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lövskogsdunge 600 m OSO Kastudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>659317</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6695143</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-07-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-07-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>79238929</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lövskog 675 m OSO Kastudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>659317</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6695143</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-07-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-07-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>80378574</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Finnsjöns östra sida 690 m OSO Kastudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>659365</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6695108</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100335413</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nybron, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>659195</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6695210</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>79238423</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Blandskog 500 m OSO Kastudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>659219</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6695264</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-07-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-07-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>80378594</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Finnsjöns östra sida 670 m OSO Kastudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>659359</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6695142</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Ängslövskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström, Jörgen Sjöström, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14157-2022 artfynd.xlsx
+++ b/artfynd/A 14157-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -813,6 +818,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80379191</t>
         </is>
       </c>
     </row>
@@ -940,6 +950,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81946451</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1046,6 +1061,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/750775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80357197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,6 +1332,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80379204</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1424,6 +1454,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79238730</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78814285</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1666,6 +1706,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80378561</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1785,6 +1830,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80378569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1894,6 +1944,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100335339</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2000,6 +2055,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2309408</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2118,6 +2178,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79238934</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2241,6 +2306,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78814233</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2355,6 +2425,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79238470</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2469,6 +2544,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79238805</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2588,6 +2668,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80378568</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2702,6 +2787,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79238905</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2820,6 +2910,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79238929</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2943,6 +3038,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80378574</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3052,6 +3152,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100335413</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3166,6 +3271,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79238423</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3285,8 +3395,37 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80378594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>